--- a/AAII_Financials/Yearly/XIACY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/XIACY_YR_FIN.xlsx
@@ -971,10 +971,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>60750500</v>
+        <v>60736800</v>
       </c>
       <c r="E17" s="3">
-        <v>46976400</v>
+        <v>47020200</v>
       </c>
       <c r="F17" s="3">
         <v>36131600</v>
@@ -1004,10 +1004,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>4628500</v>
+        <v>4642200</v>
       </c>
       <c r="E18" s="3">
-        <v>3153900</v>
+        <v>3110200</v>
       </c>
       <c r="F18" s="3">
         <v>2082200</v>
@@ -1052,10 +1052,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>351300</v>
+        <v>365000</v>
       </c>
       <c r="E20" s="3">
-        <v>-164500</v>
+        <v>-208300</v>
       </c>
       <c r="F20" s="3">
         <v>34000</v>
@@ -1448,10 +1448,10 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-351300</v>
+        <v>-365000</v>
       </c>
       <c r="E32" s="3">
-        <v>164500</v>
+        <v>208300</v>
       </c>
       <c r="F32" s="3">
         <v>-34000</v>
